--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/BLINK/SPAgent_4B_pi3x_spatial_BLINK.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/BLINK/SPAgent_4B_pi3x_spatial_BLINK.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="392">
   <si>
     <t>question</t>
   </si>
@@ -1195,12 +1195,9 @@
 &lt;answer&gt;(A) left&lt;/answer&gt;</t>
   </si>
   <si>
-    <t>The unresolved geometric quantity is the lateral displacement sign of the camera’s orbit, specifically whether the camera moved left or right around the object.
-From the images:
-- In the first image, the background is dominated by a beige tiled wall and a white sink, with no visible door frame.
-- In the second image, a wooden door frame appears on the left side, indicating the camera has moved to the left.
-This matches the hypothesis that the camera is moving clockwise (left), as the camera orbits around the object and the door frame becomes visible on the left side in the second image.
-We now verify the selected option against the object identity. The black hexagonal cup remains in the center in both images, confirming it is the target object. The change in background indicates lateral displacement consistent with a leftward camera orbit.
+    <t>The 3D reconstruction shows the camera positions relative to the scene. Cam1 (first image) is positioned to the right, looking at the cup from the right side. The second image (Cam2) shows the cup from the left, with the door frame visible on the left side. This indicates the camera moved from the right to the left around the cup.
+In the 3D diagram, the camera’s azimuth angle is -90° for Cam1, which corresponds to the right side (as per the ego-right → left-position → back-position → right-position orbit). When moving to the left, the camera should be at azimuth 0° (front), then -90° (left), then 0° (back), then 90° (right). Since the second image shows the cup from the left (door frame on left), the camera moved from Cam1 to Cam2, which is leftward.
+The 3D diagram confirms that Cam1 is on the right, and Cam2 is on the left. Therefore, the camera moved counter-clockwise (left) around the object.
 &lt;answer&gt;A&lt;/answer&gt;</t>
   </si>
   <si>
@@ -1265,18 +1262,10 @@
 &lt;answer&gt;(B) right&lt;/answer&gt;</t>
   </si>
   <si>
-    <t>We are given two images from a video capturing a static scene with a camera orbiting a bottle. The first image is from the beginning of the video, and the second is from the end. We must determine if the camera is moving clockwise (left) or counter-clockwise (right) around the object.
-We have reconstructed the scene and obtained a 3D point cloud. The key is to analyze the relative positions of the camera views and the object (the bottle) to infer the direction of motion.
-The object is the bottle. In the first image (beginning of video), the bottle is positioned such that its label is facing the camera. In the second image (end of video), the bottle has rotated relative to the camera. We must determine if this rotation corresponds to a clockwise or counter-clockwise orbit.
-We will use the "Orbit views named front/left/back/right" solver (Solver A). The camera positions are defined relative to the object. The orbit direction is determined by the sequence: front → left → back → right.
-We need to determine the lateral displacement sign (left/right) from view1 to view2. We will use the following approach:
-- Use a GLOBAL view with camera_view=false, rotation_reference_camera=1, and a substantially different nonzero angle.
-- Reproject C2-C1 into cam1's frame.
-However, since we have the 3D reconstruction and the camera positions are known, we can directly analyze the spatial relationship.
-In the first image, the bottle is on the right side of the frame. In the second image, the bottle is on the left side of the frame. This indicates that the camera has moved from a position where the bottle is on the right to a position where it is on the left. This corresponds to a counter-clockwise (right) orbit.
-We can also verify this by inspecting the forward central ray and the far scene boundary. In the first image, the camera is positioned such that the bottle is on the right. In the second image, the camera has moved to the left, indicating a counter-clockwise orbit.
-Therefore, the camera is moving right.
-&lt;answer&gt;B&lt;/answer&gt;</t>
+    <t>The unresolved geometric quantity is the **lateral displacement sign** of the camera’s orbit around the bottle, as the bag (“PANAMA”) moves from left to right between the two images, indicating a rotation direction.
+From the first image (left image), the bag is to the left of the bottle. In the second image (right image), the bag is to the right of the bottle — this is a clear lateral displacement sign change. In a counter-clockwise orbit (left), the left side of the scene moves to the right side of the scene — consistent with the bag’s position shift. Therefore, the camera is orbiting **counter-clockwise**, which is **left**.
+We verify this against object identity: the bottle remains central, and the bag’s relative position shifts from left to right — confirming the camera’s counter-clockwise motion (left).
+&lt;answer&gt;(A) left&lt;/answer&gt;</t>
   </si>
   <si>
     <t>To determine whether the camera is moving left or right around the object, we need to analyze the relative positions of the camera views. The first image is from the beginning of the video, and the second image is from the end. The camera is orbiting around a static scene, and we need to infer the direction of motion based on the change in perspective between the two images.
@@ -1762,13 +1751,6 @@
 In the ego-centered orbit view, moving from front to back is left to right. The first image is front-facing, and the second image is right-facing. Since the camera moved from front to right, this corresponds to counter-clockwise (left) motion.
 Therefore, the camera is moving left.
 &lt;answer&gt;A&lt;/answer&gt;</t>
-  </si>
-  <si>
-    <t>The 3D reconstruction shows the camera’s orbit path around the object. The first image (left) and second image (right) are aligned with the ego-right/left movement convention: front → left → back → right.
-In the 3D view, the camera’s forward central ray (from the object’s center) points along the X-axis (forward), and the scene boundary (far edge) aligns with the X-axis direction. The camera has moved from a position where the bowl is in the foreground (first image) to a position where it’s more central and the blue container and bottle are now to the left (second image).
-This movement corresponds to a counter-clockwise (left) orbit — consistent with the ego-right/left convention where left = counter-clockwise.
-The object identity (bowl, blue container, bottle) remains consistent across both images, and their relative depth and lateral position confirm the camera moved left.
-&lt;answer&gt;(A) left&lt;/answer&gt;</t>
   </si>
   <si>
     <t>The 3D reconstruction shows two camera positions: Cam1* (first image) and Cam2 (second image). In the global view, Cam1* is positioned to the left of Cam2 along the X-axis (forward direction). Since the camera is orbiting the object, and the first image is at the beginning and the second at the end, the camera must have moved from Cam1* to Cam2, which is to the right of Cam1* in the ego-right direction.
@@ -5296,7 +5278,7 @@
         <v>279</v>
       </c>
       <c r="J114" t="s">
-        <v>374</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -5322,7 +5304,7 @@
         <v>279</v>
       </c>
       <c r="J115" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -5348,7 +5330,7 @@
         <v>279</v>
       </c>
       <c r="J116" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -5374,7 +5356,7 @@
         <v>279</v>
       </c>
       <c r="J117" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -5400,7 +5382,7 @@
         <v>279</v>
       </c>
       <c r="J118" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -5452,7 +5434,7 @@
         <v>279</v>
       </c>
       <c r="J120" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -5504,7 +5486,7 @@
         <v>279</v>
       </c>
       <c r="J122" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -5530,7 +5512,7 @@
         <v>279</v>
       </c>
       <c r="J123" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -5556,7 +5538,7 @@
         <v>279</v>
       </c>
       <c r="J124" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -5582,7 +5564,7 @@
         <v>279</v>
       </c>
       <c r="J125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -5608,7 +5590,7 @@
         <v>279</v>
       </c>
       <c r="J126" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -5634,7 +5616,7 @@
         <v>279</v>
       </c>
       <c r="J127" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -5660,7 +5642,7 @@
         <v>279</v>
       </c>
       <c r="J128" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -5686,7 +5668,7 @@
         <v>279</v>
       </c>
       <c r="J129" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -5712,7 +5694,7 @@
         <v>279</v>
       </c>
       <c r="J130" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -5738,7 +5720,7 @@
         <v>279</v>
       </c>
       <c r="J131" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -5764,7 +5746,7 @@
         <v>279</v>
       </c>
       <c r="J132" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -5790,7 +5772,7 @@
         <v>279</v>
       </c>
       <c r="J133" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -5816,7 +5798,7 @@
         <v>279</v>
       </c>
       <c r="J134" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
